--- a/data/trans_orig/P05A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116844</t>
+          <t>115331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156556</t>
+          <t>156869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65930</t>
+          <t>66483</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95545</t>
+          <t>97595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190577</t>
+          <t>189481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>242197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227003</t>
+          <t>227084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271053</t>
+          <t>270781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149542</t>
+          <t>147291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184163</t>
+          <t>184385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>387795</t>
+          <t>388068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444374</t>
+          <t>444341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69420</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101754</t>
+          <t>103443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>46745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74712</t>
+          <t>74040</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121537</t>
+          <t>123586</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165998</t>
+          <t>165048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98604</t>
+          <t>98947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133649</t>
+          <t>132883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99295</t>
+          <t>96800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133068</t>
+          <t>133385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205036</t>
+          <t>204361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254564</t>
+          <t>255709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>158809</t>
+          <t>160007</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>196592</t>
+          <t>199095</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>174146</t>
+          <t>173697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212014</t>
+          <t>213089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>345785</t>
+          <t>343600</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>401472</t>
+          <t>398532</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>57792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47944</t>
+          <t>48018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75889</t>
+          <t>76184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113448</t>
+          <t>112506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160292</t>
+          <t>157189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149327</t>
+          <t>151851</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>193833</t>
+          <t>194065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>41704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64947</t>
+          <t>65546</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>199124</t>
+          <t>201262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250841</t>
+          <t>248841</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>246342</t>
+          <t>246415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295765</t>
+          <t>292017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70869</t>
+          <t>71015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96976</t>
+          <t>96004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>326521</t>
+          <t>330018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381285</t>
+          <t>380614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79654</t>
+          <t>80398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116396</t>
+          <t>115687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43348</t>
+          <t>43366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110485</t>
+          <t>109596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149404</t>
+          <t>149767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>383787</t>
+          <t>384687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>452098</t>
+          <t>451488</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>205460</t>
+          <t>204737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>255056</t>
+          <t>260010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>605072</t>
+          <t>604558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>691352</t>
+          <t>692547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>561639</t>
+          <t>561183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>630347</t>
+          <t>633275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>318624</t>
+          <t>316792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375582</t>
+          <t>373251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>899141</t>
+          <t>897898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>986628</t>
+          <t>989938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196215</t>
+          <t>195451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252191</t>
+          <t>250884</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>115619</t>
+          <t>116835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158722</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>326026</t>
+          <t>326787</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>393180</t>
+          <t>395544</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109928</t>
+          <t>112607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>148676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143026</t>
+          <t>144016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187176</t>
+          <t>189587</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264583</t>
+          <t>267538</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>322705</t>
+          <t>326076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130789</t>
+          <t>130977</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>167612</t>
+          <t>168135</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>242280</t>
+          <t>236955</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>288593</t>
+          <t>290358</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>381823</t>
+          <t>382123</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>449490</t>
+          <t>444634</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57351</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89317</t>
+          <t>87587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118635</t>
+          <t>116299</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>158730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>182771</t>
+          <t>184161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>234427</t>
+          <t>235219</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86288</t>
+          <t>88057</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119595</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>369402</t>
+          <t>375829</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>439450</t>
+          <t>437230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>473148</t>
+          <t>474309</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>547307</t>
+          <t>546523</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>134342</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168060</t>
+          <t>168614</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>582306</t>
+          <t>580968</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>649905</t>
+          <t>649872</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>724943</t>
+          <t>728065</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>806805</t>
+          <t>806317</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56156</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>195215</t>
+          <t>196328</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>249567</t>
+          <t>249213</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>239437</t>
+          <t>238758</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>294725</t>
+          <t>296447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1014967</t>
+          <t>1019036</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1124774</t>
+          <t>1127031</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>993150</t>
+          <t>999417</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1102926</t>
+          <t>1108542</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2045677</t>
+          <t>2039449</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2198310</t>
+          <t>2198595</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1538041</t>
+          <t>1541525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1651856</t>
+          <t>1651601</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1619538</t>
+          <t>1610985</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1737939</t>
+          <t>1728441</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3192352</t>
+          <t>3187881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3348124</t>
+          <t>3352921</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>545813</t>
+          <t>551755</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>639331</t>
+          <t>635619</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>606044</t>
+          <t>600634</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>697992</t>
+          <t>692586</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1179733</t>
+          <t>1180419</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1308931</t>
+          <t>1307711</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103899</t>
+          <t>102758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142951</t>
+          <t>142838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119512</t>
+          <t>120483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200826</t>
+          <t>198954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>252782</t>
+          <t>254696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>166556</t>
+          <t>166492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>208702</t>
+          <t>209121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111323</t>
+          <t>111508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147920</t>
+          <t>147832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>292127</t>
+          <t>287871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>347388</t>
+          <t>346798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108633</t>
+          <t>107567</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147550</t>
+          <t>146266</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64206</t>
+          <t>65522</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98872</t>
+          <t>95545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>183345</t>
+          <t>182479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236319</t>
+          <t>232519</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104714</t>
+          <t>104353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142504</t>
+          <t>142707</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92029</t>
+          <t>91769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129283</t>
+          <t>129943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206587</t>
+          <t>205867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259377</t>
+          <t>259949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159257</t>
+          <t>159045</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204213</t>
+          <t>203104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125755</t>
+          <t>126353</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>165114</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>297597</t>
+          <t>295192</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>355372</t>
+          <t>355185</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,25%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94171</t>
+          <t>94572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133217</t>
+          <t>131871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>65037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97823</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166784</t>
+          <t>168804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217456</t>
+          <t>222906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180285</t>
+          <t>180420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228627</t>
+          <t>227950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80179</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113097</t>
+          <t>110858</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268914</t>
+          <t>270639</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327400</t>
+          <t>328305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233620</t>
+          <t>234363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>284591</t>
+          <t>283839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88068</t>
+          <t>88993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119319</t>
+          <t>119590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329969</t>
+          <t>332484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394277</t>
+          <t>392696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145259</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188836</t>
+          <t>186962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73834</t>
+          <t>72792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,47 +5347,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>28,34%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>224150</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>199656</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>254005</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>25,36%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>22,59%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>28,74%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>224150</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>199391</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>252652</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>25,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>342280</t>
+          <t>339653</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>412606</t>
+          <t>407088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>240579</t>
+          <t>242754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>296091</t>
+          <t>294881</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>597640</t>
+          <t>601772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>688935</t>
+          <t>684329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444266</t>
+          <t>446867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>512832</t>
+          <t>517100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>301061</t>
+          <t>302185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>358842</t>
+          <t>354943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>764646</t>
+          <t>767916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>855453</t>
+          <t>853646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267465</t>
+          <t>265734</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>327878</t>
+          <t>325061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>140112</t>
+          <t>143351</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188238</t>
+          <t>188151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>423937</t>
+          <t>420575</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>500108</t>
+          <t>494849</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167323</t>
+          <t>165533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212080</t>
+          <t>211007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266067</t>
+          <t>264126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320608</t>
+          <t>321264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>442977</t>
+          <t>445097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>512385</t>
+          <t>513363</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>202197</t>
+          <t>200807</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>245458</t>
+          <t>247950</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>273390</t>
+          <t>274775</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>329601</t>
+          <t>329748</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>494042</t>
+          <t>494051</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>563600</t>
+          <t>566064</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79479</t>
+          <t>80096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114518</t>
+          <t>114383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142428</t>
+          <t>141419</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189703</t>
+          <t>187754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231496</t>
+          <t>232066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291438</t>
+          <t>289255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>75176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106036</t>
+          <t>106313</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>267685</t>
+          <t>267263</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>330007</t>
+          <t>328228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>355282</t>
+          <t>352982</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>423642</t>
+          <t>421824</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100219</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132594</t>
+          <t>133342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>470210</t>
+          <t>467714</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>533027</t>
+          <t>533302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>583849</t>
+          <t>577969</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>656377</t>
+          <t>655731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48015</t>
+          <t>47883</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74882</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>276911</t>
+          <t>279091</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>335106</t>
+          <t>340713</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331673</t>
+          <t>333216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>397379</t>
+          <t>401181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1047091</t>
+          <t>1041798</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1157145</t>
+          <t>1157113</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1104386</t>
+          <t>1107004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1219436</t>
+          <t>1221844</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2185352</t>
+          <t>2180213</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2346927</t>
+          <t>2352411</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1385523</t>
+          <t>1384968</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1504831</t>
+          <t>1506956</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1452455</t>
+          <t>1455728</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1575548</t>
+          <t>1568857</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2875141</t>
+          <t>2874987</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3040982</t>
+          <t>3045978</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>804060</t>
+          <t>808523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>907982</t>
+          <t>910063</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>801408</t>
+          <t>801510</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>903426</t>
+          <t>905835</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1635782</t>
+          <t>1635481</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1781674</t>
+          <t>1780881</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134646</t>
+          <t>135019</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177083</t>
+          <t>176880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100998</t>
+          <t>100048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135758</t>
+          <t>135150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244721</t>
+          <t>243726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>298623</t>
+          <t>299831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145917</t>
+          <t>146429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>188821</t>
+          <t>186781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126607</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163135</t>
+          <t>161447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284409</t>
+          <t>286269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341694</t>
+          <t>341088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89440</t>
+          <t>88963</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124202</t>
+          <t>127185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69510</t>
+          <t>68950</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100439</t>
+          <t>101238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168521</t>
+          <t>166906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215439</t>
+          <t>215137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102080</t>
+          <t>101510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137356</t>
+          <t>139758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128599</t>
+          <t>128061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167726</t>
+          <t>167959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240656</t>
+          <t>239990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>293021</t>
+          <t>293636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147443</t>
+          <t>146502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186809</t>
+          <t>186895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120212</t>
+          <t>119838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>157917</t>
+          <t>158696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>280016</t>
+          <t>277367</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>332686</t>
+          <t>333546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73945</t>
+          <t>73397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107340</t>
+          <t>105497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72169</t>
+          <t>71480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105487</t>
+          <t>104760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155442</t>
+          <t>153483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200579</t>
+          <t>202485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>175447</t>
+          <t>175548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>220206</t>
+          <t>218205</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54766</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80397</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>238295</t>
+          <t>238612</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>290138</t>
+          <t>289981</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186727</t>
+          <t>183397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230634</t>
+          <t>230762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53335</t>
+          <t>54083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78706</t>
+          <t>80739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>248767</t>
+          <t>249695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>300246</t>
+          <t>300256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97184</t>
+          <t>96851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134056</t>
+          <t>135384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43350</t>
+          <t>42755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126212</t>
+          <t>125581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169168</t>
+          <t>169400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>408945</t>
+          <t>408796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>473192</t>
+          <t>476009</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308778</t>
+          <t>306948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>363373</t>
+          <t>364820</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>733575</t>
+          <t>736277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>819509</t>
+          <t>823591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419670</t>
+          <t>417839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484416</t>
+          <t>486659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>280148</t>
+          <t>280034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>334521</t>
+          <t>335570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>715864</t>
+          <t>714003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>801695</t>
+          <t>802806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>224472</t>
+          <t>222251</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>280469</t>
+          <t>282203</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>154945</t>
+          <t>154780</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203167</t>
+          <t>202057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>393167</t>
+          <t>393934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>467535</t>
+          <t>471419</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224548</t>
+          <t>224408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273796</t>
+          <t>273960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>285658</t>
+          <t>288190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342420</t>
+          <t>342939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527283</t>
+          <t>530030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599273</t>
+          <t>600969</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>198931</t>
+          <t>199648</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>246110</t>
+          <t>246485</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>223568</t>
+          <t>227861</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279846</t>
+          <t>278074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>440362</t>
+          <t>440782</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>510924</t>
+          <t>513242</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125795</t>
+          <t>126625</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168466</t>
+          <t>168154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143240</t>
+          <t>143193</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>194279</t>
+          <t>190806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>283185</t>
+          <t>280558</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>349684</t>
+          <t>343484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80153</t>
+          <t>81614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113376</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>386457</t>
+          <t>386034</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>452202</t>
+          <t>453319</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>481750</t>
+          <t>479354</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>551109</t>
+          <t>551057</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>101210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132908</t>
+          <t>133966</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>406099</t>
+          <t>406425</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>474785</t>
+          <t>472168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>517640</t>
+          <t>518312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>594417</t>
+          <t>591970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>58399</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88240</t>
+          <t>86684</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>194652</t>
+          <t>191102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>249031</t>
+          <t>247386</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>261607</t>
+          <t>259370</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>322803</t>
+          <t>320959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1203915</t>
+          <t>1207643</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1313961</t>
+          <t>1321823</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1341951</t>
+          <t>1341175</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1458655</t>
+          <t>1458119</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2584830</t>
+          <t>2570300</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2744370</t>
+          <t>2740572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1280962</t>
+          <t>1274243</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1395333</t>
+          <t>1391431</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1290693</t>
+          <t>1285221</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1411201</t>
+          <t>1401044</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2601186</t>
+          <t>2604032</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2772569</t>
+          <t>2769536</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>730995</t>
+          <t>732984</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>828432</t>
+          <t>827244</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>716654</t>
+          <t>721138</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>816907</t>
+          <t>825681</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1476270</t>
+          <t>1483180</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1616926</t>
+          <t>1625433</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44652</t>
+          <t>44948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75149</t>
+          <t>75372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67694</t>
+          <t>67852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95004</t>
+          <t>93672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133002</t>
+          <t>132904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>64939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99777</t>
+          <t>98997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48207</t>
+          <t>48198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72419</t>
+          <t>72113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120634</t>
+          <t>120836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159404</t>
+          <t>161380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>342172</t>
+          <t>343317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>386111</t>
+          <t>386665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>316087</t>
+          <t>314951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>346688</t>
+          <t>347256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>670333</t>
+          <t>670726</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>723353</t>
+          <t>723906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>28536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54687</t>
+          <t>54715</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56250</t>
+          <t>56356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>68002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101566</t>
+          <t>101313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47544</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>46423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>70952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>98717</t>
+          <t>100207</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138038</t>
+          <t>139604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>332157</t>
+          <t>331648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>367950</t>
+          <t>370451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>264493</t>
+          <t>265076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>294289</t>
+          <t>294871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>607427</t>
+          <t>607730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>657686</t>
+          <t>655758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>14211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67929</t>
+          <t>68988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21703</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23717</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82202</t>
+          <t>84252</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80864</t>
+          <t>80379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101205</t>
+          <t>100734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>524801</t>
+          <t>522368</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640032</t>
+          <t>637944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122186</t>
+          <t>122693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139489</t>
+          <t>138725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654017</t>
+          <t>654933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>782101</t>
+          <t>777365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>50610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83834</t>
+          <t>85546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90720</t>
+          <t>92602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>603729</t>
+          <t>624502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151659</t>
+          <t>153205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>887537</t>
+          <t>835082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>111660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156526</t>
+          <t>159779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56303</t>
+          <t>57848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149159</t>
+          <t>146467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169090</t>
+          <t>170252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283202</t>
+          <t>281484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>809089</t>
+          <t>804961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>859463</t>
+          <t>860324</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>310964</t>
+          <t>287577</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>748165</t>
+          <t>747677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>959712</t>
+          <t>996799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1591508</t>
+          <t>1588865</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48281</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>42195</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74402</t>
+          <t>74016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74376</t>
+          <t>75018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115183</t>
+          <t>116129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49852</t>
+          <t>50539</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82681</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>106303</t>
+          <t>105734</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>355512</t>
+          <t>327937</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>170438</t>
+          <t>169561</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>427334</t>
+          <t>424488</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>354883</t>
+          <t>352073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>392684</t>
+          <t>390566</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>438730</t>
+          <t>460715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>670432</t>
+          <t>671001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>800985</t>
+          <t>813030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1045783</t>
+          <t>1046523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>37260</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35620</t>
+          <t>35587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62837</t>
+          <t>63599</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48793</t>
+          <t>49475</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>88175</t>
+          <t>85848</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39776</t>
+          <t>37532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79200</t>
+          <t>79619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112850</t>
+          <t>114388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92167</t>
+          <t>93823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137152</t>
+          <t>138185</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>182592</t>
+          <t>183554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>219767</t>
+          <t>219475</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>597601</t>
+          <t>597627</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>638357</t>
+          <t>638297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>791178</t>
+          <t>794052</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>848744</t>
+          <t>848731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>192714</t>
+          <t>204044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>299307</t>
+          <t>300909</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>304606</t>
+          <t>303781</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1148375</t>
+          <t>1111867</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>546170</t>
+          <t>553679</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1362160</t>
+          <t>1458972</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>304289</t>
+          <t>319564</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>455998</t>
+          <t>451183</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>429700</t>
+          <t>429920</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>725662</t>
+          <t>735784</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>810487</t>
+          <t>803362</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1128592</t>
+          <t>1125587</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2637753</t>
+          <t>2640692</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2882296</t>
+          <t>2869404</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2060180</t>
+          <t>2086376</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2752439</t>
+          <t>2759944</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4763967</t>
+          <t>4657067</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5509158</t>
+          <t>5480840</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115331</t>
+          <t>116156</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156869</t>
+          <t>157677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66483</t>
+          <t>65223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97595</t>
+          <t>97275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189481</t>
+          <t>190770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242197</t>
+          <t>243894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227084</t>
+          <t>226290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270781</t>
+          <t>270468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147291</t>
+          <t>148736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184385</t>
+          <t>183882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388068</t>
+          <t>388755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444341</t>
+          <t>445350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67656</t>
+          <t>68861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>103156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46745</t>
+          <t>47160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74040</t>
+          <t>73709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>123586</t>
+          <t>121325</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>165662</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98947</t>
+          <t>97483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132883</t>
+          <t>133394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96800</t>
+          <t>97583</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133385</t>
+          <t>132613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>204361</t>
+          <t>206270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255709</t>
+          <t>257238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160007</t>
+          <t>159058</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>199095</t>
+          <t>196792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>173697</t>
+          <t>174108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>213089</t>
+          <t>211037</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>343600</t>
+          <t>343747</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>398532</t>
+          <t>398227</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57792</t>
+          <t>59168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90994</t>
+          <t>90572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48018</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76184</t>
+          <t>75471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112506</t>
+          <t>114926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157189</t>
+          <t>157676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151851</t>
+          <t>150116</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>194065</t>
+          <t>194835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41704</t>
+          <t>40859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65546</t>
+          <t>65487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>201262</t>
+          <t>201274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>248841</t>
+          <t>249635</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>246415</t>
+          <t>249309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>292017</t>
+          <t>296087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71015</t>
+          <t>69783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96004</t>
+          <t>97433</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>330018</t>
+          <t>329074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>380614</t>
+          <t>381473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,86%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80398</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115687</t>
+          <t>115998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43366</t>
+          <t>44207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109596</t>
+          <t>109750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149767</t>
+          <t>151183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>384687</t>
+          <t>380087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>451488</t>
+          <t>452609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204737</t>
+          <t>205749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>260010</t>
+          <t>254579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>604558</t>
+          <t>604423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>692547</t>
+          <t>688946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>561183</t>
+          <t>560249</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>633275</t>
+          <t>632122</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316792</t>
+          <t>321088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>373251</t>
+          <t>372897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>897898</t>
+          <t>901491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>989938</t>
+          <t>987355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195451</t>
+          <t>197888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>250884</t>
+          <t>253768</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>116835</t>
+          <t>113920</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159367</t>
+          <t>157223</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>326787</t>
+          <t>325476</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>395544</t>
+          <t>392870</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112607</t>
+          <t>110559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148676</t>
+          <t>146621</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144016</t>
+          <t>145250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189587</t>
+          <t>188709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267538</t>
+          <t>264206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>326076</t>
+          <t>322788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130977</t>
+          <t>130389</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>168135</t>
+          <t>166281</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>236955</t>
+          <t>241577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>290358</t>
+          <t>289092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>382123</t>
+          <t>383749</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>444634</t>
+          <t>445787</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87587</t>
+          <t>85104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>116299</t>
+          <t>116345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158730</t>
+          <t>158607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184161</t>
+          <t>184343</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>235219</t>
+          <t>237854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88057</t>
+          <t>86974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120381</t>
+          <t>118233</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>375829</t>
+          <t>372359</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>437230</t>
+          <t>438489</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>474309</t>
+          <t>470727</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>546523</t>
+          <t>544762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134342</t>
+          <t>135706</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168614</t>
+          <t>167634</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>580968</t>
+          <t>580835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>649872</t>
+          <t>649573</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>728065</t>
+          <t>728236</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>806317</t>
+          <t>806489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33270</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>55911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>196328</t>
+          <t>196616</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>249213</t>
+          <t>248611</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>238758</t>
+          <t>235621</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>296447</t>
+          <t>294350</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1019036</t>
+          <t>1012748</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1127031</t>
+          <t>1122306</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>999417</t>
+          <t>1002116</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1108542</t>
+          <t>1106416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2039449</t>
+          <t>2045501</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2198595</t>
+          <t>2193394</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1541525</t>
+          <t>1538087</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1651601</t>
+          <t>1652453</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1610985</t>
+          <t>1612217</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1728441</t>
+          <t>1726337</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3187881</t>
+          <t>3176431</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3352921</t>
+          <t>3340420</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>551755</t>
+          <t>550873</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>635619</t>
+          <t>640591</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>600634</t>
+          <t>603896</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>692586</t>
+          <t>692874</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1180419</t>
+          <t>1177588</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1307711</t>
+          <t>1302594</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102758</t>
+          <t>104163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142838</t>
+          <t>142767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85532</t>
+          <t>84595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120483</t>
+          <t>120561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198954</t>
+          <t>198552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254696</t>
+          <t>250156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>166492</t>
+          <t>167749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209121</t>
+          <t>210096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111508</t>
+          <t>112574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147832</t>
+          <t>149440</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287871</t>
+          <t>287086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>346798</t>
+          <t>342585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107567</t>
+          <t>107713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>148978</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65522</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95545</t>
+          <t>96795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>182479</t>
+          <t>184910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232519</t>
+          <t>235440</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104353</t>
+          <t>104659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142707</t>
+          <t>144437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91769</t>
+          <t>91801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129943</t>
+          <t>128154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205867</t>
+          <t>202416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259949</t>
+          <t>261087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159045</t>
+          <t>160268</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>203104</t>
+          <t>204411</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126353</t>
+          <t>126023</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165114</t>
+          <t>165605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>295192</t>
+          <t>296889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>355185</t>
+          <t>355810</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94572</t>
+          <t>92734</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131871</t>
+          <t>132511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>64985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97702</t>
+          <t>97820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168804</t>
+          <t>167005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222906</t>
+          <t>215865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180420</t>
+          <t>177715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227950</t>
+          <t>230596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80755</t>
+          <t>79166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110858</t>
+          <t>110049</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>270639</t>
+          <t>272069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>328305</t>
+          <t>326876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>234363</t>
+          <t>229770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>283839</t>
+          <t>282909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88993</t>
+          <t>88305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119590</t>
+          <t>120090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>332484</t>
+          <t>330311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392696</t>
+          <t>389602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143604</t>
+          <t>144537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186962</t>
+          <t>190328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>47339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72792</t>
+          <t>74114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199656</t>
+          <t>195351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254005</t>
+          <t>250633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>339653</t>
+          <t>339770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>407088</t>
+          <t>407965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>242754</t>
+          <t>244869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294881</t>
+          <t>298347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>601772</t>
+          <t>599417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>684329</t>
+          <t>687979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>446867</t>
+          <t>446633</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517100</t>
+          <t>517570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302185</t>
+          <t>302406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>354943</t>
+          <t>357516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>767916</t>
+          <t>767623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>853646</t>
+          <t>853629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>265734</t>
+          <t>267416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>325061</t>
+          <t>325890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143351</t>
+          <t>142188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>188151</t>
+          <t>188839</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>420575</t>
+          <t>417405</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494849</t>
+          <t>495865</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165533</t>
+          <t>165161</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211007</t>
+          <t>209837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264126</t>
+          <t>266020</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>321264</t>
+          <t>319478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>445097</t>
+          <t>443272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513363</t>
+          <t>517473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>200807</t>
+          <t>203461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>247950</t>
+          <t>246028</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>274775</t>
+          <t>274466</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>329748</t>
+          <t>328918</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>494051</t>
+          <t>489127</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>566064</t>
+          <t>564678</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>79963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114383</t>
+          <t>115968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>141419</t>
+          <t>141463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187754</t>
+          <t>187650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232066</t>
+          <t>230421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289255</t>
+          <t>291661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75176</t>
+          <t>76815</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106313</t>
+          <t>106532</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>267263</t>
+          <t>269041</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>328228</t>
+          <t>329646</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>352982</t>
+          <t>355979</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>421824</t>
+          <t>423803</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100158</t>
+          <t>100093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133342</t>
+          <t>133007</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>467714</t>
+          <t>467155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>533302</t>
+          <t>535541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>577969</t>
+          <t>580049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>655731</t>
+          <t>651895</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47883</t>
+          <t>46097</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73623</t>
+          <t>75825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>279091</t>
+          <t>275455</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>339235</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>333216</t>
+          <t>332872</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401181</t>
+          <t>400748</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1041798</t>
+          <t>1043099</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1157113</t>
+          <t>1162715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1107004</t>
+          <t>1104622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1221844</t>
+          <t>1221842</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2180213</t>
+          <t>2187968</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2352411</t>
+          <t>2347064</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1384968</t>
+          <t>1388590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1506956</t>
+          <t>1509935</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1455728</t>
+          <t>1450488</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1568857</t>
+          <t>1571232</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2874987</t>
+          <t>2875949</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3045978</t>
+          <t>3053737</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>808523</t>
+          <t>806153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>910063</t>
+          <t>909506</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>801510</t>
+          <t>800725</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>905835</t>
+          <t>913670</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1635481</t>
+          <t>1631491</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1780881</t>
+          <t>1784322</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135019</t>
+          <t>134935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176880</t>
+          <t>174504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100048</t>
+          <t>98775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135150</t>
+          <t>137022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243726</t>
+          <t>245135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299831</t>
+          <t>300569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146429</t>
+          <t>146197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186781</t>
+          <t>187492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126337</t>
+          <t>126682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161447</t>
+          <t>164425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286269</t>
+          <t>281994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341088</t>
+          <t>339947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88963</t>
+          <t>89352</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127185</t>
+          <t>126515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101238</t>
+          <t>101405</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>166906</t>
+          <t>166944</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215137</t>
+          <t>215941</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101510</t>
+          <t>103525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139758</t>
+          <t>139069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128061</t>
+          <t>128257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167959</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>239990</t>
+          <t>241050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>293636</t>
+          <t>292693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146502</t>
+          <t>146503</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186895</t>
+          <t>186751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119838</t>
+          <t>119311</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158696</t>
+          <t>157719</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>277367</t>
+          <t>278385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>333546</t>
+          <t>331512</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73397</t>
+          <t>73199</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105497</t>
+          <t>106922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71480</t>
+          <t>70208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104760</t>
+          <t>104276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153483</t>
+          <t>153945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202485</t>
+          <t>200722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>175548</t>
+          <t>175033</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218205</t>
+          <t>220018</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79945</t>
+          <t>81294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>238612</t>
+          <t>238522</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>289981</t>
+          <t>290544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183397</t>
+          <t>185098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230762</t>
+          <t>232308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54083</t>
+          <t>53297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80739</t>
+          <t>81268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249695</t>
+          <t>249331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>300256</t>
+          <t>301575</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96851</t>
+          <t>95316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135384</t>
+          <t>133732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>22868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>44504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125581</t>
+          <t>124593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169400</t>
+          <t>167186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>408796</t>
+          <t>410981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>476009</t>
+          <t>479229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>306948</t>
+          <t>307206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>364820</t>
+          <t>363566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>736277</t>
+          <t>734223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>823591</t>
+          <t>822410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417839</t>
+          <t>421000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>486659</t>
+          <t>488950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>280034</t>
+          <t>280698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>335570</t>
+          <t>334955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>714003</t>
+          <t>712794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>802806</t>
+          <t>800818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222251</t>
+          <t>225926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>282203</t>
+          <t>279446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>155058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202057</t>
+          <t>202377</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>393934</t>
+          <t>395114</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>471419</t>
+          <t>467675</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224408</t>
+          <t>224550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273960</t>
+          <t>274574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288190</t>
+          <t>288321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342939</t>
+          <t>341542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530030</t>
+          <t>527376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600969</t>
+          <t>602043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199648</t>
+          <t>193548</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>246485</t>
+          <t>245085</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>227861</t>
+          <t>226595</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>278074</t>
+          <t>280662</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>440782</t>
+          <t>440867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>513242</t>
+          <t>513094</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126625</t>
+          <t>127933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168154</t>
+          <t>172731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143193</t>
+          <t>142601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190806</t>
+          <t>189462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280558</t>
+          <t>283322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>343484</t>
+          <t>345726</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81614</t>
+          <t>80404</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112186</t>
+          <t>111652</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>386034</t>
+          <t>386193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>453319</t>
+          <t>454165</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>479354</t>
+          <t>476460</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>551057</t>
+          <t>553357</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101210</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133966</t>
+          <t>133769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>406425</t>
+          <t>406378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>472168</t>
+          <t>470995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>518312</t>
+          <t>520470</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>591970</t>
+          <t>598195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58399</t>
+          <t>58274</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>86684</t>
+          <t>87881</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>191102</t>
+          <t>191358</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>247386</t>
+          <t>246759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>259370</t>
+          <t>259325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320959</t>
+          <t>321742</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1207643</t>
+          <t>1208037</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1321823</t>
+          <t>1319462</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1341175</t>
+          <t>1340103</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1458119</t>
+          <t>1460096</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2570300</t>
+          <t>2579344</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2740572</t>
+          <t>2737706</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1274243</t>
+          <t>1273003</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1391431</t>
+          <t>1383046</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1285221</t>
+          <t>1291836</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1401044</t>
+          <t>1406825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2604032</t>
+          <t>2608450</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2769536</t>
+          <t>2774976</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>732984</t>
+          <t>734075</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>827244</t>
+          <t>831686</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>721138</t>
+          <t>719677</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>825681</t>
+          <t>821621</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,47 +10597,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1546234</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>1469333</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>1617863</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>22,44%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>23,48%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1546234</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>1483180</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1625433</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>58403</t>
+          <t>62928</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44948</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75372</t>
+          <t>81070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>61041</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67852</t>
+          <t>74538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>112657</t>
+          <t>123969</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93672</t>
+          <t>105991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132904</t>
+          <t>145577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81262</t>
+          <t>91959</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64939</t>
+          <t>73707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98997</t>
+          <t>112282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58828</t>
+          <t>67925</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72113</t>
+          <t>82490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>140090</t>
+          <t>159884</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120836</t>
+          <t>139625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161380</t>
+          <t>185905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>365147</t>
+          <t>395308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>343317</t>
+          <t>373960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>386665</t>
+          <t>418038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>333044</t>
+          <t>358013</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>314951</t>
+          <t>341120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>347256</t>
+          <t>374699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>698190</t>
+          <t>753321</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>670726</t>
+          <t>723078</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>723906</t>
+          <t>778444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504812</t>
+          <t>550195</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>504812</t>
+          <t>550195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504812</t>
+          <t>550195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>950937</t>
+          <t>1037174</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>950937</t>
+          <t>1037174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>950937</t>
+          <t>1037174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>39884</t>
+          <t>40991</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43940</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>37556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56356</t>
+          <t>61821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>83823</t>
+          <t>89642</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68002</t>
+          <t>72775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101313</t>
+          <t>108298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60123</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46808</t>
+          <t>51028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77241</t>
+          <t>80858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57739</t>
+          <t>65197</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>53577</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70952</t>
+          <t>78359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>117862</t>
+          <t>129604</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100207</t>
+          <t>110247</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>139604</t>
+          <t>151919</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>352207</t>
+          <t>377815</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>331648</t>
+          <t>357129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>370451</t>
+          <t>393873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>280901</t>
+          <t>309295</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>265076</t>
+          <t>292217</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>294871</t>
+          <t>322268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,27 +11758,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>633108</t>
+          <t>687110</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>607730</t>
+          <t>660655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>655758</t>
+          <t>711914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39564</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68988</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21490</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>54819</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24988</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84252</t>
+          <t>73877</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46485</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>67552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28213</t>
+          <t>32242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67253</t>
+          <t>76517</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>61780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100734</t>
+          <t>96188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>582214</t>
+          <t>378157</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522368</t>
+          <t>359113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>637944</t>
+          <t>395883</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>130889</t>
+          <t>146752</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122693</t>
+          <t>137091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138725</t>
+          <t>155863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>713103</t>
+          <t>524908</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654933</t>
+          <t>501359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777365</t>
+          <t>544684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66223</t>
+          <t>76178</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>58809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85546</t>
+          <t>97721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>282197</t>
+          <t>86411</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92602</t>
+          <t>71943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>624502</t>
+          <t>102099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>348421</t>
+          <t>162589</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153205</t>
+          <t>139362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>835082</t>
+          <t>186667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>132870</t>
+          <t>150510</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111660</t>
+          <t>129629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159779</t>
+          <t>177702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>110368</t>
+          <t>130643</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57848</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146467</t>
+          <t>150609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>243238</t>
+          <t>281152</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170252</t>
+          <t>253533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>281484</t>
+          <t>312449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>834541</t>
+          <t>902951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>804961</t>
+          <t>871952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>860324</t>
+          <t>928357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>584297</t>
+          <t>642889</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>287577</t>
+          <t>620315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>747677</t>
+          <t>664349</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1418838</t>
+          <t>1545840</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>996799</t>
+          <t>1508812</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1588865</t>
+          <t>1582372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033635</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033635</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033635</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>976862</t>
+          <t>859943</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>976862</t>
+          <t>859943</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>976862</t>
+          <t>859943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010497</t>
+          <t>1989582</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010497</t>
+          <t>1989582</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2010497</t>
+          <t>1989582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>47135</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49219</t>
+          <t>62823</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>57943</t>
+          <t>69014</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42195</t>
+          <t>56094</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74016</t>
+          <t>85624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>94215</t>
+          <t>116149</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75018</t>
+          <t>98998</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116129</t>
+          <t>138838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64800</t>
+          <t>73112</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50539</t>
+          <t>58933</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>92943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>173485</t>
+          <t>123398</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>107805</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>327937</t>
+          <t>142026</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>238285</t>
+          <t>196510</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169561</t>
+          <t>171128</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>424488</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>373974</t>
+          <t>447717</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>352073</t>
+          <t>423403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>390566</t>
+          <t>467172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>607100</t>
+          <t>635464</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>460715</t>
+          <t>614074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>671001</t>
+          <t>655245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>981074</t>
+          <t>1083181</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>813030</t>
+          <t>1052001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1046523</t>
+          <t>1112273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>838529</t>
+          <t>827876</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>838529</t>
+          <t>827876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>838529</t>
+          <t>827876</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1313574</t>
+          <t>1395840</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313574</t>
+          <t>1395840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1313574</t>
+          <t>1395840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18054</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>35552</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>48118</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63599</t>
+          <t>67881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>66172</t>
+          <t>69199</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49475</t>
+          <t>50632</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85848</t>
+          <t>89052</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>94953</t>
+          <t>104350</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79619</t>
+          <t>87593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114388</t>
+          <t>123214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>112759</t>
+          <t>121292</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93823</t>
+          <t>98863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138185</t>
+          <t>144736</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>204647</t>
+          <t>201874</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>183554</t>
+          <t>182386</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>219475</t>
+          <t>217195</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>618300</t>
+          <t>689143</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>597627</t>
+          <t>668214</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>638297</t>
+          <t>712177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>822947</t>
+          <t>891018</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>794052</t>
+          <t>859957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>848731</t>
+          <t>917794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>258401</t>
+          <t>286094</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>204044</t>
+          <t>253978</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>300909</t>
+          <t>327677</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>501706</t>
+          <t>333137</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>303781</t>
+          <t>302774</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1111867</t>
+          <t>365688</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>760106</t>
+          <t>619231</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>553679</t>
+          <t>575786</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1458972</t>
+          <t>664789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>403346</t>
+          <t>449934</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>319564</t>
+          <t>410847</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>451183</t>
+          <t>499939</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>516141</t>
+          <t>515026</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>429920</t>
+          <t>481901</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>735784</t>
+          <t>557423</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>919486</t>
+          <t>964960</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>803362</t>
+          <t>906609</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1125587</t>
+          <t>1023445</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2712730</t>
+          <t>2703821</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2640692</t>
+          <t>2646262</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2869404</t>
+          <t>2755319</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2554531</t>
+          <t>2781556</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2086376</t>
+          <t>2731878</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2759944</t>
+          <t>2827286</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5267261</t>
+          <t>5485377</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4657067</t>
+          <t>5415795</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5480840</t>
+          <t>5556352</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3374477</t>
+          <t>3439849</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3374477</t>
+          <t>3439849</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3374477</t>
+          <t>3439849</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3572377</t>
+          <t>3629719</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3572377</t>
+          <t>3629719</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3572377</t>
+          <t>3629719</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6946854</t>
+          <t>7069568</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6946854</t>
+          <t>7069568</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6946854</t>
+          <t>7069568</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
